--- a/Preuves/Registre_des _preuves.xlsx
+++ b/Preuves/Registre_des _preuves.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAURENT\Desktop\NextStep\Preuves\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAURENT\Desktop\NextOri\Preuves\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66D028F-9EC0-4697-B771-5EC01F0F15B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1281D0EB-C5A8-4442-AB2D-D7984815F606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{1439711C-300C-4E54-B98F-8A27498AAEC6}"/>
   </bookViews>
@@ -45,9 +45,6 @@
     <t>Formulaire orientation _ KoboToolbox.pdf</t>
   </si>
   <si>
-    <t>Bureau/NextStep/Preuves/Formulaires enquetes</t>
-  </si>
-  <si>
     <t>Formulaire_orientation_-_all_versions_-_labels_-_2026-06-28-12-15-41.xlsx</t>
   </si>
   <si>
@@ -75,9 +72,6 @@
     <t>NextStep_Presentation.pptx</t>
   </si>
   <si>
-    <t>Bureau/NextStep/Preuves/Documents</t>
-  </si>
-  <si>
     <t>Ancien formulaire kobotoolbox</t>
   </si>
   <si>
@@ -96,9 +90,6 @@
     <t>Gmail - Lien pour accession à NextStep du groupe 5 pour Madame Raissa .pdf</t>
   </si>
   <si>
-    <t>Bureau/NextStep/Preuves/Preuves diverses</t>
-  </si>
-  <si>
     <t>Mail envoyé à notre prof de culture entrepreneurial Mme Raissa Avaligbe</t>
   </si>
   <si>
@@ -112,6 +103,15 @@
   </si>
   <si>
     <t>Cahier des charge .docx</t>
+  </si>
+  <si>
+    <t>Bureau/NextOri/Preuves/Preuves diverses</t>
+  </si>
+  <si>
+    <t>Bureau/NextOri/Cahier des charges/Anciens Documents</t>
+  </si>
+  <si>
+    <t>Bureau/NextOri/Formulaires enquetes/KoboToolbox</t>
   </si>
 </sst>
 </file>
@@ -170,14 +170,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,7 +495,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.7109375" customWidth="1"/>
     <col min="5" max="5" width="68.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -522,13 +521,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3">
         <v>46107</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -539,16 +538,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3">
         <v>46107</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -556,16 +555,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3">
         <v>46107</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -573,16 +572,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3">
         <v>46107</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -590,16 +589,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3">
         <v>46107</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -607,16 +606,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3">
         <v>46107</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -624,16 +623,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3">
         <v>46107</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -641,14 +640,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -656,14 +655,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -671,14 +670,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -686,14 +685,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -701,14 +700,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -716,33 +715,33 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3">
         <v>46093</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>25</v>
+      <c r="B15" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="C15" s="3">
         <v>46199</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
